--- a/exports/KPITTECH_full_report.xlsx
+++ b/exports/KPITTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>11.43</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>682</v>
+        <v>630.5</v>
       </c>
       <c r="I2" t="n">
         <v>655.2829999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.82</v>
+        <v>-14.78</v>
       </c>
       <c r="L2" t="n">
-        <v>9.85</v>
+        <v>16.88</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>7.04</v>
       </c>
       <c r="O2" t="n">
         <v>5.25</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>19.81</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>580</v>
+        <v>596.1</v>
       </c>
       <c r="I3" t="n">
         <v>582.0739318640326</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K3" t="n">
-        <v>8.01</v>
+        <v>5.46</v>
       </c>
       <c r="L3" t="n">
         <v>10.81</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>10.02</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>599</v>
+        <v>581.6</v>
       </c>
       <c r="I4" t="n">
         <v>590.0670214880508</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>0.49</v>
+        <v>-2.43</v>
       </c>
       <c r="L4" t="n">
         <v>6.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>4.84</v>
       </c>
       <c r="O4" t="n">
         <v>1.72</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.77</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>522.55</v>
+        <v>565.85</v>
       </c>
       <c r="I5" t="n">
         <v>560.6864357780104</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>10.15</v>
+        <v>2.71</v>
       </c>
       <c r="L5" t="n">
         <v>2.3</v>
@@ -726,7 +785,7 @@
         <v>1.93</v>
       </c>
       <c r="N5" t="n">
-        <v>1.38</v>
+        <v>11.74</v>
       </c>
       <c r="O5" t="n">
         <v>-4.84</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>13.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>527.3</v>
+        <v>509</v>
       </c>
       <c r="I6" t="n">
         <v>514.0142370198116</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.81</v>
+        <v>-10.05</v>
       </c>
       <c r="L6" t="n">
-        <v>10.7</v>
+        <v>10.83</v>
       </c>
       <c r="M6" t="n">
         <v>3.65</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.43</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>475.8</v>
+        <v>509.5</v>
       </c>
       <c r="I7" t="n">
         <v>509.1844455072288</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>6.52</v>
+        <v>-0.1</v>
       </c>
       <c r="L7" t="n">
         <v>4.7</v>
@@ -840,7 +923,7 @@
         <v>2.34</v>
       </c>
       <c r="N7" t="n">
-        <v>3.16</v>
+        <v>9.77</v>
       </c>
       <c r="O7" t="n">
         <v>-3.16</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>13.47</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>511</v>
+        <v>491.3</v>
       </c>
       <c r="I8" t="n">
         <v>505.4492427170595</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>0.29</v>
+        <v>-3.57</v>
       </c>
       <c r="L8" t="n">
         <v>4.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.95</v>
+        <v>4.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.71</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>9.77</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>499</v>
+        <v>510.1</v>
       </c>
       <c r="I9" t="n">
         <v>502.3342175879689</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.57</v>
+        <v>-3.83</v>
       </c>
       <c r="L9" t="n">
-        <v>4.21</v>
+        <v>5.98</v>
       </c>
       <c r="M9" t="n">
         <v>3.38</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.52</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>659.5</v>
+        <v>629.9</v>
       </c>
       <c r="I10" t="n">
         <v>633.9251435677993</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>113.1666666666667</v>
+        <v>114</v>
       </c>
       <c r="K10" t="n">
-        <v>29.29</v>
+        <v>23.49</v>
       </c>
       <c r="L10" t="n">
         <v>5.9</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.59</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>653.5</v>
+        <v>698.05</v>
       </c>
       <c r="I11" t="n">
         <v>696.6219727021852</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.75</v>
+        <v>-10.82</v>
       </c>
       <c r="L11" t="n">
-        <v>5.99</v>
+        <v>12.08</v>
       </c>
       <c r="M11" t="n">
         <v>0.86</v>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>8.83</v>
       </c>
       <c r="O11" t="n">
         <v>-2.35</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.54</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>681.65</v>
+        <v>675.9</v>
       </c>
       <c r="I12" t="n">
         <v>678.1820680447997</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.35</v>
+        <v>-3.17</v>
       </c>
       <c r="L12" t="n">
         <v>5.96</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.24</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44887.55208333334</v>
+        <v>44888.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>684</v>
+        <v>715.5</v>
       </c>
       <c r="I13" t="n">
         <v>709.6918138449229</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2</v>
+        <v>-5.86</v>
       </c>
       <c r="L13" t="n">
-        <v>4.07</v>
+        <v>6.52</v>
       </c>
       <c r="M13" t="n">
         <v>2.55</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>6.28</v>
       </c>
       <c r="O13" t="n">
         <v>-1.79</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.09</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44907.38541666666</v>
+        <v>44907.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>693.95</v>
+        <v>683</v>
       </c>
       <c r="I14" t="n">
         <v>691.0367576521828</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.01</v>
+        <v>-4.54</v>
       </c>
       <c r="L14" t="n">
-        <v>4.25</v>
+        <v>4.92</v>
       </c>
       <c r="M14" t="n">
         <v>0.39</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.39</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44911.55208333334</v>
+        <v>44914.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>702.6</v>
+        <v>710.9</v>
       </c>
       <c r="I15" t="n">
         <v>709.0897707965767</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.87</v>
+        <v>-4.08</v>
       </c>
       <c r="L15" t="n">
         <v>5.52</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>711.9</v>
+        <v>671.85</v>
       </c>
       <c r="I16" t="n">
         <v>676.1933675034811</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0.14</v>
+        <v>-5.49</v>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>5.74</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>1.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0.96</v>
+        <v>5.62</v>
       </c>
       <c r="O16" t="n">
         <v>1.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>10.69</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44932.38541666666</v>
+        <v>44932.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>687.85</v>
+        <v>715</v>
       </c>
       <c r="I17" t="n">
         <v>713.5092736728695</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.38</v>
+        <v>-6.42</v>
       </c>
       <c r="L17" t="n">
-        <v>6.97</v>
+        <v>7.16</v>
       </c>
       <c r="M17" t="n">
         <v>2.02</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>818.85</v>
+        <v>791</v>
       </c>
       <c r="I18" t="n">
         <v>799.4370904068718</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>65.83333333333333</v>
+        <v>66</v>
       </c>
       <c r="K18" t="n">
-        <v>14.52</v>
+        <v>10.63</v>
       </c>
       <c r="L18" t="n">
         <v>5.29</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.66</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44999.55208333334</v>
+        <v>45000.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>782.75</v>
+        <v>832.8</v>
       </c>
       <c r="I19" t="n">
         <v>828.4286764311466</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>1.04</v>
+        <v>-5.28</v>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>5.94</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
         <v>-4.23</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>10.23</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>864.1</v>
+        <v>814</v>
       </c>
       <c r="I20" t="n">
         <v>856.1496960588403</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>3.76</v>
+        <v>-2.26</v>
       </c>
       <c r="L20" t="n">
-        <v>6.27</v>
+        <v>8.74</v>
       </c>
       <c r="M20" t="n">
         <v>0.49</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>13.88</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45042.38541666666</v>
+        <v>45042.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>878.6</v>
+        <v>904</v>
       </c>
       <c r="I21" t="n">
         <v>897.9229035616145</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.94</v>
+        <v>-11.06</v>
       </c>
       <c r="L21" t="n">
-        <v>10.2</v>
+        <v>12.29</v>
       </c>
       <c r="M21" t="n">
         <v>0.61</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1098.95</v>
+        <v>1038.85</v>
       </c>
       <c r="I22" t="n">
         <v>1074.093296975298</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>21.57</v>
+        <v>14.92</v>
       </c>
       <c r="L22" t="n">
         <v>5.08</v>
@@ -1695,7 +1958,7 @@
         <v>0.37</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>5.36</v>
       </c>
       <c r="O22" t="n">
         <v>5.98</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.12</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1071.1</v>
+        <v>1078.6</v>
       </c>
       <c r="I23" t="n">
         <v>1074.243854749568</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.1</v>
+        <v>-3.83</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.52</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1148</v>
+        <v>1137.9</v>
       </c>
       <c r="I24" t="n">
         <v>1142.746337386467</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>6.43</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
         <v>3.69</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.63</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1130</v>
+        <v>1153</v>
       </c>
       <c r="I25" t="n">
         <v>1130.971021590666</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.33</v>
       </c>
       <c r="L25" t="n">
         <v>3.96</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.99</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1158</v>
+        <v>1140.05</v>
       </c>
       <c r="I26" t="n">
         <v>1142.115869677524</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.43</v>
+        <v>-1.12</v>
       </c>
       <c r="L26" t="n">
         <v>4.31</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45229.55208333334</v>
+        <v>45230.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1187.15</v>
+        <v>1224.75</v>
       </c>
       <c r="I27" t="n">
         <v>1200.43402470731</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.13</v>
+        <v>-7.43</v>
       </c>
       <c r="L27" t="n">
-        <v>6.44</v>
+        <v>10.06</v>
       </c>
       <c r="M27" t="n">
-        <v>0.62</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
         <v>5.15</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>9.33</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1510</v>
+        <v>1446.45</v>
       </c>
       <c r="I28" t="n">
         <v>1470.023439958843</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>23.29</v>
+        <v>18.1</v>
       </c>
       <c r="L28" t="n">
         <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0.32</v>
+        <v>1.6</v>
       </c>
       <c r="N28" t="n">
         <v>6.48</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.18</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1488</v>
+        <v>1540</v>
       </c>
       <c r="I29" t="n">
         <v>1515.431820551687</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.87</v>
+        <v>-6.47</v>
       </c>
       <c r="L29" t="n">
-        <v>4.67</v>
+        <v>7.15</v>
       </c>
       <c r="M29" t="n">
         <v>1.44</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45315.55208333334</v>
+        <v>45316.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1506</v>
+        <v>1399.4</v>
       </c>
       <c r="I30" t="n">
         <v>1493.626696844028</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.21</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>7.4</v>
+        <v>9.59</v>
       </c>
       <c r="M30" t="n">
         <v>1.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.93</v>
+        <v>5.89</v>
       </c>
       <c r="O30" t="n">
         <v>1.95</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>11.47</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1456.05</v>
+        <v>1534.5</v>
       </c>
       <c r="I31" t="n">
         <v>1500.759044903098</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.05</v>
+        <v>-9.65</v>
       </c>
       <c r="L31" t="n">
-        <v>7.51</v>
+        <v>11.47</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>6.39</v>
       </c>
       <c r="O31" t="n">
         <v>-5.89</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45343.38541666666</v>
+        <v>45343.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1595</v>
+        <v>1572</v>
       </c>
       <c r="I32" t="n">
         <v>1579.501839041349</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>3.94</v>
+        <v>2.44</v>
       </c>
       <c r="L32" t="n">
         <v>4.59</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.23</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.38541666666</v>
+        <v>45378.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1471.55</v>
+        <v>1491.5</v>
       </c>
       <c r="I33" t="n">
         <v>1473.704812243089</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>6.39</v>
+        <v>5.12</v>
       </c>
       <c r="L33" t="n">
         <v>2.69</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1430.95</v>
+        <v>1416.7</v>
       </c>
       <c r="I34" t="n">
         <v>1422.321002145995</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.06</v>
+        <v>-5.02</v>
       </c>
       <c r="L34" t="n">
         <v>5.39</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45411.38541666666</v>
+        <v>45411.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1413.5</v>
+        <v>1509.75</v>
       </c>
       <c r="I35" t="n">
         <v>1443.470602874047</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>0.23</v>
+        <v>-6.57</v>
       </c>
       <c r="L35" t="n">
-        <v>2.77</v>
+        <v>7.96</v>
       </c>
       <c r="M35" t="n">
         <v>1.7</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.23</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1479</v>
+        <v>1461</v>
       </c>
       <c r="I36" t="n">
         <v>1477.81987919766</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.04</v>
+        <v>-3.23</v>
       </c>
       <c r="L36" t="n">
         <v>6.54</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.29</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45462.55208333334</v>
+        <v>45463.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1515.1</v>
+        <v>1549.1</v>
       </c>
       <c r="I37" t="n">
         <v>1524.209577667857</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.7</v>
+        <v>-6.03</v>
       </c>
       <c r="L37" t="n">
-        <v>5.07</v>
+        <v>6.23</v>
       </c>
       <c r="M37" t="n">
         <v>4.67</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45510.38541666666</v>
+        <v>45510.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1726.55</v>
+        <v>1693</v>
       </c>
       <c r="I38" t="n">
         <v>1720.686044922741</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>11.46</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>2.72</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1844.1</v>
+        <v>1861.3</v>
       </c>
       <c r="I39" t="n">
         <v>1857.853557861926</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.92</v>
+        <v>-9.94</v>
       </c>
       <c r="L39" t="n">
-        <v>12.17</v>
+        <v>12.76</v>
       </c>
       <c r="M39" t="n">
         <v>2.19</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>6.3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1775.85</v>
+        <v>1747.95</v>
       </c>
       <c r="I40" t="n">
         <v>1752.874509382686</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.59</v>
+        <v>-6.09</v>
       </c>
       <c r="L40" t="n">
-        <v>5.93</v>
+        <v>6.23</v>
       </c>
       <c r="M40" t="n">
-        <v>0.38</v>
+        <v>0.89</v>
       </c>
       <c r="N40" t="n">
         <v>3.02</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.49</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45546.55208333334</v>
+        <v>45547.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1795</v>
+        <v>1838.55</v>
       </c>
       <c r="I41" t="n">
         <v>1802.89925983798</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.69</v>
+        <v>-5.18</v>
       </c>
       <c r="L41" t="n">
-        <v>2.86</v>
+        <v>5.84</v>
       </c>
       <c r="M41" t="n">
         <v>0.95</v>
       </c>
       <c r="N41" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
         <v>-1.46</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.46</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1740</v>
+        <v>1726</v>
       </c>
       <c r="I42" t="n">
         <v>1737.264662539699</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.36</v>
+        <v>-6.12</v>
       </c>
       <c r="L42" t="n">
-        <v>5.85</v>
+        <v>6.39</v>
       </c>
       <c r="M42" t="n">
         <v>-0</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.61</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1719</v>
+        <v>1754.2</v>
       </c>
       <c r="I43" t="n">
         <v>1726.891699342389</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>0.41</v>
+        <v>-1.63</v>
       </c>
       <c r="L43" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
         <v>1.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.24</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45587.38541666666</v>
+        <v>45587.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1698.95</v>
+        <v>1681</v>
       </c>
       <c r="I44" t="n">
         <v>1687.057652629209</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.15</v>
+        <v>-4.17</v>
       </c>
       <c r="L44" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="M44" t="n">
         <v>0.5600000000000001</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.63</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1368</v>
+        <v>1412.1</v>
       </c>
       <c r="I45" t="n">
         <v>1385.303895465081</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>18.62</v>
+        <v>16</v>
       </c>
       <c r="L45" t="n">
         <v>3.7</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1467.55</v>
+        <v>1449.95</v>
       </c>
       <c r="I46" t="n">
         <v>1462.171070450414</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>3.93</v>
+        <v>2.68</v>
       </c>
       <c r="L46" t="n">
         <v>5.11</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.03</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45686.38541666666</v>
+        <v>45686.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1338.5</v>
+        <v>1377.1</v>
       </c>
       <c r="I47" t="n">
         <v>1372.044368414104</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>39.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="K47" t="n">
-        <v>7.69</v>
+        <v>5.02</v>
       </c>
       <c r="L47" t="n">
         <v>3.45</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.78</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45701.38541666666</v>
+        <v>45701.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1359.6</v>
+        <v>1338.7</v>
       </c>
       <c r="I48" t="n">
         <v>1346.864041303366</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.27</v>
+        <v>-2.79</v>
       </c>
       <c r="L48" t="n">
         <v>3.98</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1209</v>
+        <v>1286.55</v>
       </c>
       <c r="I49" t="n">
         <v>1272.07343040224</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>9.69</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
         <v>1.78</v>
       </c>
       <c r="M49" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="N49" t="n">
-        <v>1.1</v>
+        <v>5.73</v>
       </c>
       <c r="O49" t="n">
         <v>-1.24</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.12</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1233.5</v>
+        <v>1219.4</v>
       </c>
       <c r="I50" t="n">
         <v>1223.363007968743</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.12</v>
+        <v>-5.22</v>
       </c>
       <c r="L50" t="n">
         <v>5.58</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1281</v>
+        <v>1309.15</v>
       </c>
       <c r="I51" t="n">
         <v>1305.977865444532</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.05</v>
+        <v>-7.36</v>
       </c>
       <c r="L51" t="n">
-        <v>7.35</v>
+        <v>7.76</v>
       </c>
       <c r="M51" t="n">
         <v>1.1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1308</v>
+        <v>1270</v>
       </c>
       <c r="I52" t="n">
         <v>1292.215402039463</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.09</v>
+        <v>-2.99</v>
       </c>
       <c r="L52" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="M52" t="n">
         <v>2.05</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.52</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45769.55208333334</v>
+        <v>45770.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1162.5</v>
+        <v>1234.9</v>
       </c>
       <c r="I53" t="n">
         <v>1193.76689106162</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>8.460000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="L53" t="n">
         <v>3.38</v>
@@ -3462,7 +4097,7 @@
         <v>3.96</v>
       </c>
       <c r="N53" t="n">
-        <v>3.31</v>
+        <v>5.55</v>
       </c>
       <c r="O53" t="n">
         <v>-2.87</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.44</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1391.7</v>
+        <v>1314.2</v>
       </c>
       <c r="I54" t="n">
         <v>1342.82127431311</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K54" t="n">
-        <v>12.7</v>
+        <v>6.42</v>
       </c>
       <c r="L54" t="n">
         <v>4.64</v>
@@ -3519,7 +4166,7 @@
         <v>2.38</v>
       </c>
       <c r="N54" t="n">
-        <v>2.04</v>
+        <v>6.23</v>
       </c>
       <c r="O54" t="n">
         <v>5.55</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45868.38541666666</v>
+        <v>45868.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1214.3</v>
+        <v>1263</v>
       </c>
       <c r="I55" t="n">
         <v>1251.408970233793</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L55" t="n">
         <v>3.99</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.6</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.38541666666</v>
+        <v>45923.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1257.8</v>
+        <v>1250.8</v>
       </c>
       <c r="I56" t="n">
         <v>1254.896338679133</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>54.83333333333334</v>
+        <v>55</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.41</v>
+        <v>-0.97</v>
       </c>
       <c r="L56" t="n">
         <v>7.56</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>4.91</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45954.55208333334</v>
+        <v>45957.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1179</v>
+        <v>1210.7</v>
       </c>
       <c r="I57" t="n">
         <v>1200.397422393399</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>5.74</v>
+        <v>3.21</v>
       </c>
       <c r="L57" t="n">
         <v>2.33</v>
       </c>
       <c r="M57" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="N57" t="n">
         <v>3.57</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1159</v>
+        <v>1152.2</v>
       </c>
       <c r="I58" t="n">
         <v>1152.34650515221</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.27</v>
+        <v>-4.83</v>
       </c>
       <c r="L58" t="n">
-        <v>5.55</v>
+        <v>5.76</v>
       </c>
       <c r="M58" t="n">
         <v>0.72</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.38541666666</v>
+        <v>45972.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1196.9</v>
+        <v>1205.2</v>
       </c>
       <c r="I59" t="n">
         <v>1200.327719308612</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.88</v>
+        <v>-4.6</v>
       </c>
       <c r="L59" t="n">
-        <v>5.06</v>
+        <v>5.57</v>
       </c>
       <c r="M59" t="n">
         <v>0.33</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.4</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45982.38541666666</v>
+        <v>45982.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1175.9</v>
+        <v>1172.9</v>
       </c>
       <c r="I60" t="n">
         <v>1175.074907718603</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.43</v>
+        <v>-2.68</v>
       </c>
       <c r="L60" t="n">
-        <v>2.65</v>
+        <v>3.49</v>
       </c>
       <c r="M60" t="n">
         <v>0.49</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.61</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45989.55208333334</v>
+        <v>45992.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1221.5</v>
+        <v>1251.4</v>
       </c>
       <c r="I61" t="n">
         <v>1226.945259045041</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.14</v>
+        <v>-6.69</v>
       </c>
       <c r="L61" t="n">
-        <v>4.77</v>
+        <v>7.22</v>
       </c>
       <c r="M61" t="n">
         <v>0.23</v>
       </c>
       <c r="N61" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O61" t="n">
         <v>-2.26</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.35</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46000.38541666666</v>
+        <v>46000.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1216</v>
+        <v>1205.5</v>
       </c>
       <c r="I62" t="n">
         <v>1212.687096406638</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.83</v>
+        <v>-3.67</v>
       </c>
       <c r="L62" t="n">
         <v>4.59</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.65</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>1190.5</v>
+        <v>1222.8</v>
       </c>
       <c r="I63" t="n">
         <v>1211.635259159145</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>1.24</v>
+        <v>-1.44</v>
       </c>
       <c r="L63" t="n">
         <v>2.86</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>6.32</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1190</v>
+        <v>1168.7</v>
       </c>
       <c r="I64" t="n">
         <v>1175.258808988484</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.68</v>
+        <v>-4.42</v>
       </c>
       <c r="L64" t="n">
-        <v>3.29</v>
+        <v>4.62</v>
       </c>
       <c r="M64" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="N64" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="O64" t="n">
         <v>5.41</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>6.09</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46029.38541666666</v>
+        <v>46029.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1189.1</v>
+        <v>1208</v>
       </c>
       <c r="I65" t="n">
         <v>1189.344464181655</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.75</v>
+        <v>-3.36</v>
       </c>
       <c r="L65" t="n">
-        <v>2.59</v>
+        <v>4.19</v>
       </c>
       <c r="M65" t="n">
         <v>0.42</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1160.9</v>
+        <v>1134.4</v>
       </c>
       <c r="I66" t="n">
         <v>1136.21398401286</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.9</v>
+        <v>-6.09</v>
       </c>
       <c r="L66" t="n">
-        <v>4.47</v>
+        <v>6.8</v>
       </c>
       <c r="M66" t="n">
         <v>0.95</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>654.55</v>
+        <v>692.7</v>
       </c>
       <c r="I67" t="n">
         <v>690.3882501905194</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K67" t="n">
-        <v>42.3</v>
+        <v>38.94</v>
       </c>
       <c r="L67" t="n">
         <v>3.04</v>
@@ -4260,7 +5063,7 @@
         <v>5.78</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O67" t="n">
         <v>-2.66</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.51</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>730</v>
+        <v>694.35</v>
       </c>
       <c r="I68" t="n">
         <v>698.4691515544546</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K68" t="n">
-        <v>5.38</v>
+        <v>0.24</v>
       </c>
       <c r="L68" t="n">
         <v>8.619999999999999</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>10.76</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46142.55208333334</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>758</v>
+        <v>765.3</v>
       </c>
       <c r="I69" t="n">
         <v>758.2189823519336</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.17</v>
+        <v>-10.22</v>
       </c>
       <c r="L69" t="n">
-        <v>10.49</v>
+        <v>11.92</v>
       </c>
       <c r="M69" t="n">
-        <v>0.48</v>
+        <v>1.19</v>
       </c>
       <c r="N69" t="n">
         <v>3.67</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>7.03</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>749.45</v>
+        <v>716.9</v>
       </c>
       <c r="I70" t="n">
         <v>721.3739159974963</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.07</v>
+        <v>-6.32</v>
       </c>
       <c r="L70" t="n">
-        <v>5.59</v>
+        <v>7.33</v>
       </c>
       <c r="M70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N70" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="O70" t="n">
         <v>1.45</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>13.38</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>750</v>
+        <v>756.5</v>
       </c>
       <c r="I71" t="n">
         <v>755.0057066576906</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.62</v>
+        <v>-5.52</v>
       </c>
       <c r="L71" t="n">
-        <v>6.14</v>
+        <v>6.64</v>
       </c>
       <c r="M71" t="n">
         <v>0.67</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.66</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>752</v>
+        <v>748.3</v>
       </c>
       <c r="I72" t="n">
         <v>749.5819006288306</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.59</v>
+        <v>-1.08</v>
       </c>
       <c r="L72" t="n">
         <v>1.6</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>9.26</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46227.38541666666</v>
+        <v>46227.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>577</v>
+        <v>583.3</v>
       </c>
       <c r="I73" t="n">
         <v>580.2560620065015</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K73" t="n">
-        <v>22.89</v>
+        <v>22.05</v>
       </c>
       <c r="L73" t="n">
         <v>3.43</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.12</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46252.55208333334</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>597.5</v>
+        <v>590.1</v>
       </c>
       <c r="I74" t="n">
         <v>592.7257016650697</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K74" t="n">
-        <v>2.43</v>
+        <v>1.17</v>
       </c>
       <c r="L74" t="n">
         <v>2.17</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.03</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46262.38541666666</v>
+        <v>46262.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>608.45</v>
+        <v>610.65</v>
       </c>
       <c r="I75" t="n">
         <v>610.3656628719758</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.11</v>
+        <v>-3.48</v>
       </c>
       <c r="L75" t="n">
         <v>3.96</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.33</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46269.38541666666</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>579.15</v>
+        <v>575.55</v>
       </c>
       <c r="I76" t="n">
         <v>578.1144715293889</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.16</v>
+        <v>-5.75</v>
       </c>
       <c r="L76" t="n">
-        <v>5.26</v>
+        <v>5.84</v>
       </c>
       <c r="M76" t="n">
         <v>0.37</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>5.19</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>481.25</v>
+        <v>509.9</v>
       </c>
       <c r="I77" t="n">
         <v>504.4725801282445</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K77" t="n">
-        <v>16.38</v>
+        <v>11.41</v>
       </c>
       <c r="L77" t="n">
         <v>0.9399999999999999</v>
@@ -4830,7 +5753,7 @@
         <v>1.54</v>
       </c>
       <c r="N77" t="n">
-        <v>1.81</v>
+        <v>6.75</v>
       </c>
       <c r="O77" t="n">
         <v>-1.41</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4890,6 +5825,12 @@
       <c r="Q78" t="n">
         <v>20</v>
       </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6992,7 +7933,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="6">
@@ -7002,7 +7943,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="7">
@@ -7012,7 +7953,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -7022,7 +7963,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -7032,7 +7973,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.3</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -7042,7 +7983,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="11">
@@ -7052,7 +7993,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -7062,7 +8003,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -7072,7 +8013,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -7082,7 +8023,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.13</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="15">
@@ -7092,7 +8033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.81</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="16">
@@ -7102,7 +8043,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.45</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="17">
@@ -7112,7 +8053,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.3</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="18">
@@ -7122,7 +8063,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.7</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="19">
@@ -7132,7 +8073,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.97</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="20">
@@ -7142,7 +8083,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.62</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="21">
@@ -7152,7 +8093,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.17</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="22">
@@ -7162,7 +8103,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -7172,7 +8113,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -7182,7 +8123,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="25">
@@ -7202,7 +8143,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.82</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="27">
@@ -7222,7 +8163,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
